--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135843483</v>
       </c>
       <c r="B3" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135843499</v>
       </c>
       <c r="B4" t="n">
-        <v>92262</v>
+        <v>92264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135840237</v>
       </c>
       <c r="B5" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843496</v>
       </c>
       <c r="B6" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135843498</v>
       </c>
       <c r="B7" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135843494</v>
       </c>
       <c r="B8" t="n">
-        <v>87457</v>
+        <v>87458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135843487</v>
       </c>
       <c r="B9" t="n">
-        <v>92713</v>
+        <v>92715</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>135840239</v>
       </c>
       <c r="B18" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135840205</v>
       </c>
       <c r="B19" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135840240</v>
       </c>
       <c r="B20" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135840225</v>
       </c>
       <c r="B21" t="n">
-        <v>98139</v>
+        <v>98141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135843487</v>
+        <v>136007932</v>
       </c>
       <c r="B9" t="n">
-        <v>92715</v>
+        <v>89292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,37 +1476,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5454</v>
+        <v>4412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergsmannijärvi, T lm</t>
+          <t>bergmannivaara, T lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752195</v>
+        <v>752115</v>
       </c>
       <c r="R9" t="n">
-        <v>7519938</v>
+        <v>7519834</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,27 +1560,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843487</t>
+          <t>https://artportalen.se/Sighting/136007932</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135840201</v>
+        <v>135843487</v>
       </c>
       <c r="B10" t="n">
-        <v>78844</v>
+        <v>92715</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,37 +1588,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>5454</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Bergsmannijärvi, T lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752073</v>
+        <v>752195</v>
       </c>
       <c r="R10" t="n">
-        <v>7519813</v>
+        <v>7519938</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,24 +1672,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840201</t>
+          <t>https://artportalen.se/Sighting/135843487</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135840206</v>
+        <v>135840201</v>
       </c>
       <c r="B11" t="n">
         <v>78844</v>
@@ -1724,13 +1724,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>752102</v>
+        <v>752073</v>
       </c>
       <c r="R11" t="n">
-        <v>7519878</v>
+        <v>7519813</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,16 +1795,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840206</t>
+          <t>https://artportalen.se/Sighting/135840201</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135840203</v>
+        <v>135840206</v>
       </c>
       <c r="B12" t="n">
-        <v>79198</v>
+        <v>78844</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1812,21 +1812,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752097</v>
+        <v>752102</v>
       </c>
       <c r="R12" t="n">
-        <v>7519837</v>
+        <v>7519878</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,16 +1907,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840203</t>
+          <t>https://artportalen.se/Sighting/135840206</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135840204</v>
+        <v>135840203</v>
       </c>
       <c r="B13" t="n">
-        <v>80060</v>
+        <v>79198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752089</v>
+        <v>752097</v>
       </c>
       <c r="R13" t="n">
-        <v>7519839</v>
+        <v>7519837</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2019,38 +2019,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840204</t>
+          <t>https://artportalen.se/Sighting/135840203</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135840211</v>
+        <v>135840204</v>
       </c>
       <c r="B14" t="n">
-        <v>80450</v>
+        <v>80060</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2060,13 +2060,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>752189</v>
+        <v>752089</v>
       </c>
       <c r="R14" t="n">
-        <v>7519891</v>
+        <v>7519839</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,13 +2131,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840211</t>
+          <t>https://artportalen.se/Sighting/135840204</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135840213</v>
+        <v>135840211</v>
       </c>
       <c r="B15" t="n">
         <v>80450</v>
@@ -2172,13 +2172,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752162</v>
+        <v>752189</v>
       </c>
       <c r="R15" t="n">
-        <v>7519893</v>
+        <v>7519891</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,16 +2243,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840213</t>
+          <t>https://artportalen.se/Sighting/135840211</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135840210</v>
+        <v>135840213</v>
       </c>
       <c r="B16" t="n">
-        <v>80568</v>
+        <v>80450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752141</v>
+        <v>752162</v>
       </c>
       <c r="R16" t="n">
-        <v>7519886</v>
+        <v>7519893</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,58 +2355,54 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840210</t>
+          <t>https://artportalen.se/Sighting/135840213</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135834021</v>
+        <v>135840210</v>
       </c>
       <c r="B17" t="n">
-        <v>58084</v>
+        <v>80568</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, Bergsmannivaara, T lm</t>
+          <t>Bergsmannivaara, T lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>752226</v>
+        <v>752141</v>
       </c>
       <c r="R17" t="n">
-        <v>7519924</v>
+        <v>7519886</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2435,7 +2431,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2441,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,65 +2456,69 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135834021</t>
+          <t>https://artportalen.se/Sighting/135840210</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135840239</v>
+        <v>135834021</v>
       </c>
       <c r="B18" t="n">
-        <v>106398</v>
+        <v>58084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Bergsmannivaara, Bergsmannivaara, T lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>752120</v>
+        <v>752226</v>
       </c>
       <c r="R18" t="n">
-        <v>7519555</v>
+        <v>7519924</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,27 +2572,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840239</t>
+          <t>https://artportalen.se/Sighting/135834021</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135840205</v>
+        <v>135840239</v>
       </c>
       <c r="B19" t="n">
-        <v>98144</v>
+        <v>106398</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2600,21 +2600,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,13 +2624,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>752084</v>
+        <v>752120</v>
       </c>
       <c r="R19" t="n">
-        <v>7519866</v>
+        <v>7519555</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2689,22 +2689,22 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840205</t>
+          <t>https://artportalen.se/Sighting/135840239</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135840240</v>
+        <v>135840205</v>
       </c>
       <c r="B20" t="n">
-        <v>98138</v>
+        <v>98144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,16 +2712,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752042</v>
+        <v>752084</v>
       </c>
       <c r="R20" t="n">
-        <v>7519458</v>
+        <v>7519866</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,22 +2801,22 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840240</t>
+          <t>https://artportalen.se/Sighting/135840205</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135840225</v>
+        <v>135840240</v>
       </c>
       <c r="B21" t="n">
-        <v>98141</v>
+        <v>98138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752025</v>
+        <v>752042</v>
       </c>
       <c r="R21" t="n">
-        <v>7519756</v>
+        <v>7519458</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,7 +2919,343 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135840240</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135840225</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98141</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>752025</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7519756</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135840225</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136007917</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98141</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>bergmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>752019</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7519745</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136007917</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136007924</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>bergmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>751708</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7519876</v>
+      </c>
+      <c r="S24" t="n">
+        <v>8</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136007924</t>
         </is>
       </c>
     </row>
@@ -2945,6 +3281,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840242</v>
       </c>
       <c r="B2" t="n">
-        <v>83433</v>
+        <v>83435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +795,7 @@
         <v>135843483</v>
       </c>
       <c r="B3" t="n">
-        <v>92396</v>
+        <v>92408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135843499</v>
       </c>
       <c r="B4" t="n">
-        <v>92264</v>
+        <v>92278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135840237</v>
       </c>
       <c r="B5" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
         <v>135843496</v>
       </c>
       <c r="B6" t="n">
-        <v>92178</v>
+        <v>92192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135843498</v>
       </c>
       <c r="B7" t="n">
-        <v>92178</v>
+        <v>92192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135843494</v>
       </c>
       <c r="B8" t="n">
-        <v>87458</v>
+        <v>87460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136007932</v>
       </c>
       <c r="B9" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135843487</v>
       </c>
       <c r="B10" t="n">
-        <v>92715</v>
+        <v>92730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135840201</v>
       </c>
       <c r="B11" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1804,7 +1804,7 @@
         <v>135840206</v>
       </c>
       <c r="B12" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1916,7 +1916,7 @@
         <v>135840203</v>
       </c>
       <c r="B13" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2028,7 +2028,7 @@
         <v>135840204</v>
       </c>
       <c r="B14" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2140,7 +2140,7 @@
         <v>135840211</v>
       </c>
       <c r="B15" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2252,7 +2252,7 @@
         <v>135840213</v>
       </c>
       <c r="B16" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2364,7 +2364,7 @@
         <v>135840210</v>
       </c>
       <c r="B17" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2476,7 +2476,7 @@
         <v>135834021</v>
       </c>
       <c r="B18" t="n">
-        <v>58084</v>
+        <v>58086</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135840239</v>
       </c>
       <c r="B19" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
         <v>135840205</v>
       </c>
       <c r="B20" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2816,7 +2816,7 @@
         <v>135840240</v>
       </c>
       <c r="B21" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2928,7 +2928,7 @@
         <v>135840225</v>
       </c>
       <c r="B22" t="n">
-        <v>98141</v>
+        <v>98158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3040,7 +3040,7 @@
         <v>136007917</v>
       </c>
       <c r="B23" t="n">
-        <v>98141</v>
+        <v>98158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136007924</v>
       </c>
       <c r="B24" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, per-erik mukka, Anna Öhlund</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Christina Boyd, Stefan Andersson, Anna Öhlund, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840242</v>
       </c>
       <c r="B2" t="n">
-        <v>83435</v>
+        <v>83436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135843483</v>
       </c>
       <c r="B3" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135843499</v>
       </c>
       <c r="B4" t="n">
-        <v>92278</v>
+        <v>92279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135840237</v>
       </c>
       <c r="B5" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843496</v>
       </c>
       <c r="B6" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135843498</v>
       </c>
       <c r="B7" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135843494</v>
       </c>
       <c r="B8" t="n">
-        <v>87460</v>
+        <v>87461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136007932</v>
       </c>
       <c r="B9" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135843487</v>
       </c>
       <c r="B10" t="n">
-        <v>92730</v>
+        <v>92731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135840201</v>
       </c>
       <c r="B11" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135840206</v>
       </c>
       <c r="B12" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135840203</v>
       </c>
       <c r="B13" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135840204</v>
       </c>
       <c r="B14" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135840211</v>
       </c>
       <c r="B15" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135840213</v>
       </c>
       <c r="B16" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135840210</v>
       </c>
       <c r="B17" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135840239</v>
       </c>
       <c r="B19" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135840205</v>
       </c>
       <c r="B20" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135840240</v>
       </c>
       <c r="B21" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135840225</v>
       </c>
       <c r="B22" t="n">
-        <v>98158</v>
+        <v>98159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136007917</v>
       </c>
       <c r="B23" t="n">
-        <v>98158</v>
+        <v>98159</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136007924</v>
       </c>
       <c r="B24" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135843483</v>
       </c>
       <c r="B3" t="n">
-        <v>92409</v>
+        <v>92410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135843499</v>
       </c>
       <c r="B4" t="n">
-        <v>92279</v>
+        <v>92280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135840237</v>
       </c>
       <c r="B5" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843496</v>
       </c>
       <c r="B6" t="n">
-        <v>92193</v>
+        <v>92194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135843498</v>
       </c>
       <c r="B7" t="n">
-        <v>92193</v>
+        <v>92194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135843494</v>
       </c>
       <c r="B8" t="n">
-        <v>87461</v>
+        <v>87462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136007932</v>
       </c>
       <c r="B9" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135843487</v>
       </c>
       <c r="B10" t="n">
-        <v>92731</v>
+        <v>92732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135840239</v>
       </c>
       <c r="B19" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135840205</v>
       </c>
       <c r="B20" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135840240</v>
       </c>
       <c r="B21" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135840225</v>
       </c>
       <c r="B22" t="n">
-        <v>98159</v>
+        <v>98160</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136007917</v>
       </c>
       <c r="B23" t="n">
-        <v>98159</v>
+        <v>98160</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840242</v>
       </c>
       <c r="B2" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135843483</v>
       </c>
       <c r="B3" t="n">
-        <v>92410</v>
+        <v>92411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135843499</v>
       </c>
       <c r="B4" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135840237</v>
       </c>
       <c r="B5" t="n">
-        <v>91988</v>
+        <v>91989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843496</v>
       </c>
       <c r="B6" t="n">
-        <v>92194</v>
+        <v>92195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135843498</v>
       </c>
       <c r="B7" t="n">
-        <v>92194</v>
+        <v>92195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135843494</v>
       </c>
       <c r="B8" t="n">
-        <v>87462</v>
+        <v>87463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136007932</v>
       </c>
       <c r="B9" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135843487</v>
       </c>
       <c r="B10" t="n">
-        <v>92732</v>
+        <v>92733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135840201</v>
       </c>
       <c r="B11" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135840206</v>
       </c>
       <c r="B12" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135840203</v>
       </c>
       <c r="B13" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135840204</v>
       </c>
       <c r="B14" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135840211</v>
       </c>
       <c r="B15" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135840213</v>
       </c>
       <c r="B16" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135840210</v>
       </c>
       <c r="B17" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135834021</v>
       </c>
       <c r="B18" t="n">
-        <v>58086</v>
+        <v>58087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135840239</v>
       </c>
       <c r="B19" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135840205</v>
       </c>
       <c r="B20" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135840240</v>
       </c>
       <c r="B21" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135840225</v>
       </c>
       <c r="B22" t="n">
-        <v>98160</v>
+        <v>98161</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136007917</v>
       </c>
       <c r="B23" t="n">
-        <v>98160</v>
+        <v>98161</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136007924</v>
       </c>
       <c r="B24" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840242</v>
       </c>
       <c r="B2" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135843483</v>
       </c>
       <c r="B3" t="n">
-        <v>92411</v>
+        <v>92417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135843499</v>
       </c>
       <c r="B4" t="n">
-        <v>92281</v>
+        <v>92287</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135840237</v>
       </c>
       <c r="B5" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843496</v>
       </c>
       <c r="B6" t="n">
-        <v>92195</v>
+        <v>92201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135843498</v>
       </c>
       <c r="B7" t="n">
-        <v>92195</v>
+        <v>92201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135843494</v>
       </c>
       <c r="B8" t="n">
-        <v>87463</v>
+        <v>87469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136007932</v>
       </c>
       <c r="B9" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135843487</v>
       </c>
       <c r="B10" t="n">
-        <v>92733</v>
+        <v>92739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135840201</v>
       </c>
       <c r="B11" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135840206</v>
       </c>
       <c r="B12" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135840203</v>
       </c>
       <c r="B13" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135840204</v>
       </c>
       <c r="B14" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135840211</v>
       </c>
       <c r="B15" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135840213</v>
       </c>
       <c r="B16" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135840210</v>
       </c>
       <c r="B17" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135834021</v>
       </c>
       <c r="B18" t="n">
-        <v>58087</v>
+        <v>58091</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135840239</v>
       </c>
       <c r="B19" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135840205</v>
       </c>
       <c r="B20" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135840240</v>
       </c>
       <c r="B21" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135840225</v>
       </c>
       <c r="B22" t="n">
-        <v>98161</v>
+        <v>98167</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136007917</v>
       </c>
       <c r="B23" t="n">
-        <v>98161</v>
+        <v>98167</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136007924</v>
       </c>
       <c r="B24" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840242</v>
       </c>
       <c r="B2" t="n">
-        <v>83441</v>
+        <v>83442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135843483</v>
       </c>
       <c r="B3" t="n">
-        <v>92417</v>
+        <v>92418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135843499</v>
       </c>
       <c r="B4" t="n">
-        <v>92287</v>
+        <v>92288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135840237</v>
       </c>
       <c r="B5" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843496</v>
       </c>
       <c r="B6" t="n">
-        <v>92201</v>
+        <v>92202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135843498</v>
       </c>
       <c r="B7" t="n">
-        <v>92201</v>
+        <v>92202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135843494</v>
       </c>
       <c r="B8" t="n">
-        <v>87469</v>
+        <v>87470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136007932</v>
       </c>
       <c r="B9" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135843487</v>
       </c>
       <c r="B10" t="n">
-        <v>92739</v>
+        <v>92740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135840201</v>
       </c>
       <c r="B11" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135840206</v>
       </c>
       <c r="B12" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135840203</v>
       </c>
       <c r="B13" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135840204</v>
       </c>
       <c r="B14" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135840211</v>
       </c>
       <c r="B15" t="n">
-        <v>80458</v>
+        <v>80459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135840213</v>
       </c>
       <c r="B16" t="n">
-        <v>80458</v>
+        <v>80459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135840210</v>
       </c>
       <c r="B17" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135834021</v>
       </c>
       <c r="B18" t="n">
-        <v>58091</v>
+        <v>58092</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135840239</v>
       </c>
       <c r="B19" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135840205</v>
       </c>
       <c r="B20" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135840240</v>
       </c>
       <c r="B21" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135840225</v>
       </c>
       <c r="B22" t="n">
-        <v>98167</v>
+        <v>98168</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136007917</v>
       </c>
       <c r="B23" t="n">
-        <v>98167</v>
+        <v>98168</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136007924</v>
       </c>
       <c r="B24" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840242</v>
       </c>
       <c r="B2" t="n">
-        <v>83442</v>
+        <v>83446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135843483</v>
       </c>
       <c r="B3" t="n">
-        <v>92418</v>
+        <v>92424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135843499</v>
       </c>
       <c r="B4" t="n">
-        <v>92288</v>
+        <v>92294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135840237</v>
       </c>
       <c r="B5" t="n">
-        <v>91996</v>
+        <v>92002</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843496</v>
       </c>
       <c r="B6" t="n">
-        <v>92202</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135843498</v>
       </c>
       <c r="B7" t="n">
-        <v>92202</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135843494</v>
       </c>
       <c r="B8" t="n">
-        <v>87470</v>
+        <v>87476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136007932</v>
       </c>
       <c r="B9" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135843487</v>
       </c>
       <c r="B10" t="n">
-        <v>92740</v>
+        <v>92746</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135840201</v>
       </c>
       <c r="B11" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135840206</v>
       </c>
       <c r="B12" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135840203</v>
       </c>
       <c r="B13" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135840204</v>
       </c>
       <c r="B14" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135840211</v>
       </c>
       <c r="B15" t="n">
-        <v>80459</v>
+        <v>80463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135840213</v>
       </c>
       <c r="B16" t="n">
-        <v>80459</v>
+        <v>80463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135840210</v>
       </c>
       <c r="B17" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135840239</v>
       </c>
       <c r="B19" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135840205</v>
       </c>
       <c r="B20" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135840240</v>
       </c>
       <c r="B21" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135840225</v>
       </c>
       <c r="B22" t="n">
-        <v>98168</v>
+        <v>98179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136007917</v>
       </c>
       <c r="B23" t="n">
-        <v>98168</v>
+        <v>98179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136007924</v>
       </c>
       <c r="B24" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840242</v>
       </c>
       <c r="B2" t="n">
-        <v>83446</v>
+        <v>83452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135843483</v>
       </c>
       <c r="B3" t="n">
-        <v>92424</v>
+        <v>92431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135843499</v>
       </c>
       <c r="B4" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135840237</v>
       </c>
       <c r="B5" t="n">
-        <v>92002</v>
+        <v>92009</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843496</v>
       </c>
       <c r="B6" t="n">
-        <v>92208</v>
+        <v>92215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135843498</v>
       </c>
       <c r="B7" t="n">
-        <v>92208</v>
+        <v>92215</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135843494</v>
       </c>
       <c r="B8" t="n">
-        <v>87476</v>
+        <v>87483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136007932</v>
       </c>
       <c r="B9" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135843487</v>
       </c>
       <c r="B10" t="n">
-        <v>92746</v>
+        <v>92753</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135840201</v>
       </c>
       <c r="B11" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135840206</v>
       </c>
       <c r="B12" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135840203</v>
       </c>
       <c r="B13" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135840204</v>
       </c>
       <c r="B14" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135840211</v>
       </c>
       <c r="B15" t="n">
-        <v>80463</v>
+        <v>80469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135840213</v>
       </c>
       <c r="B16" t="n">
-        <v>80463</v>
+        <v>80469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135840210</v>
       </c>
       <c r="B17" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135834021</v>
       </c>
       <c r="B18" t="n">
-        <v>58092</v>
+        <v>58097</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135840239</v>
       </c>
       <c r="B19" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135840205</v>
       </c>
       <c r="B20" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135840240</v>
       </c>
       <c r="B21" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135840225</v>
       </c>
       <c r="B22" t="n">
-        <v>98179</v>
+        <v>98192</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136007917</v>
       </c>
       <c r="B23" t="n">
-        <v>98179</v>
+        <v>98192</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136007924</v>
       </c>
       <c r="B24" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135843483</v>
       </c>
       <c r="B3" t="n">
-        <v>92431</v>
+        <v>92432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Stefan Andersson, Christina Boyd, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -907,7 +907,7 @@
         <v>135843499</v>
       </c>
       <c r="B4" t="n">
-        <v>92301</v>
+        <v>92302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Anna Öhlund, per-erik mukka, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
         <v>135840237</v>
       </c>
       <c r="B5" t="n">
-        <v>92009</v>
+        <v>92010</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843496</v>
       </c>
       <c r="B6" t="n">
-        <v>92215</v>
+        <v>92216</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Anna Öhlund, Christina Boyd, Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
         <v>135843498</v>
       </c>
       <c r="B7" t="n">
-        <v>92215</v>
+        <v>92216</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Anna Öhlund, Christina Boyd, Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Stefan Andersson, Christina Boyd, Anna Öhlund, per-erik mukka</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
         <v>136007932</v>
       </c>
       <c r="B9" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135843487</v>
       </c>
       <c r="B10" t="n">
-        <v>92753</v>
+        <v>92754</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Anna Öhlund, Christina Boyd, Stefan Andersson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
         <v>135840239</v>
       </c>
       <c r="B19" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135840205</v>
       </c>
       <c r="B20" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135840240</v>
       </c>
       <c r="B21" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135840225</v>
       </c>
       <c r="B22" t="n">
-        <v>98192</v>
+        <v>98193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136007917</v>
       </c>
       <c r="B23" t="n">
-        <v>98192</v>
+        <v>98193</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135840242</v>
       </c>
       <c r="B2" t="n">
-        <v>83452</v>
+        <v>83465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135843483</v>
       </c>
       <c r="B3" t="n">
-        <v>92432</v>
+        <v>92445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Christina Boyd, Anna Öhlund, per-erik mukka</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -907,7 +907,7 @@
         <v>135843499</v>
       </c>
       <c r="B4" t="n">
-        <v>92302</v>
+        <v>92315</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Öhlund, per-erik mukka, Christina Boyd, Stefan Andersson</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
         <v>135840237</v>
       </c>
       <c r="B5" t="n">
-        <v>92010</v>
+        <v>92023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135843496</v>
       </c>
       <c r="B6" t="n">
-        <v>92216</v>
+        <v>92229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Öhlund, Christina Boyd, Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
         <v>135843498</v>
       </c>
       <c r="B7" t="n">
-        <v>92216</v>
+        <v>92229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Öhlund, Christina Boyd, Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
         <v>135843494</v>
       </c>
       <c r="B8" t="n">
-        <v>87483</v>
+        <v>87496</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Christina Boyd, Anna Öhlund, per-erik mukka</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
         <v>136007932</v>
       </c>
       <c r="B9" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135843487</v>
       </c>
       <c r="B10" t="n">
-        <v>92754</v>
+        <v>92767</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Öhlund, Christina Boyd, Stefan Andersson, per-erik mukka</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1692,7 +1692,7 @@
         <v>135840201</v>
       </c>
       <c r="B11" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135840206</v>
       </c>
       <c r="B12" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135840203</v>
       </c>
       <c r="B13" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135840204</v>
       </c>
       <c r="B14" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135840211</v>
       </c>
       <c r="B15" t="n">
-        <v>80469</v>
+        <v>80482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135840213</v>
       </c>
       <c r="B16" t="n">
-        <v>80469</v>
+        <v>80482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135840210</v>
       </c>
       <c r="B17" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135834021</v>
       </c>
       <c r="B18" t="n">
-        <v>58097</v>
+        <v>58110</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135840239</v>
       </c>
       <c r="B19" t="n">
-        <v>106454</v>
+        <v>106467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135840205</v>
       </c>
       <c r="B20" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135840240</v>
       </c>
       <c r="B21" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135840225</v>
       </c>
       <c r="B22" t="n">
-        <v>98193</v>
+        <v>98206</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136007917</v>
       </c>
       <c r="B23" t="n">
-        <v>98193</v>
+        <v>98206</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136007924</v>
       </c>
       <c r="B24" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>136007932</v>
       </c>
       <c r="B9" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136007917</v>
       </c>
       <c r="B23" t="n">
-        <v>98206</v>
+        <v>98207</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136007924</v>
       </c>
       <c r="B24" t="n">
-        <v>79496</v>
+        <v>79497</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
